--- a/shinsei-generator/output/result.xlsx
+++ b/shinsei-generator/output/result.xlsx
@@ -413,103 +413,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:C27"/>
+  <dimension ref="E5:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="3">
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>山田 設計子</t>
+    <row r="5">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>タナカ タロウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>タナカ タロウ</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>150-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>田中 太郎</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>東京都渋谷区神南一丁目2番3号</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>150-0001</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>東京都渋谷区神南一丁目2番3号</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>03-1234-5678</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" t="n">
         <v>165</v>
       </c>
     </row>
-    <row r="15">
-      <c r="C15" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="n">
+    <row r="30">
+      <c r="H30" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="21">
-      <c r="C21" t="n">
+    <row r="33">
+      <c r="E33" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="E49" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
-    <row r="22">
-      <c r="C22" t="n">
-        <v>33.33</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="n">
+    <row r="50">
+      <c r="E50" t="n">
         <v>59.45</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
+    <row r="54">
+      <c r="F54" t="inlineStr">
         <is>
           <t>1階</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="J54" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
+    <row r="55">
+      <c r="F55" t="inlineStr">
         <is>
           <t>2階</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="J55" t="n">
         <v>43.1</v>
       </c>
     </row>

--- a/shinsei-generator/output/result.xlsx
+++ b/shinsei-generator/output/result.xlsx
@@ -413,46 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="E5:J55"/>
+  <dimension ref="F5:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="5">
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>タナカ タロウ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>田中 太郎</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>150-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>東京都渋谷区神南一丁目2番3号</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>03-1234-5678</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>165</v>
       </c>
     </row>
@@ -462,17 +462,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="E33" t="n">
+      <c r="I33" t="n">
         <v>33.33</v>
       </c>
     </row>
     <row r="49">
-      <c r="E49" t="n">
+      <c r="I49" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
     <row r="50">
-      <c r="E50" t="n">
+      <c r="I50" t="n">
         <v>59.45</v>
       </c>
     </row>
@@ -482,7 +482,7 @@
           <t>1階</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>55</v>
       </c>
     </row>
@@ -492,7 +492,7 @@
           <t>2階</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>43.1</v>
       </c>
     </row>
